--- a/Datasets/Bookstores/bookstores.xlsx
+++ b/Datasets/Bookstores/bookstores.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3832D3-A4E2-40B9-A542-2C7F3E12D41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E1046A-7CF2-42CC-852F-AD67DE417259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25335" yWindow="90" windowWidth="24990" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="960" windowWidth="24990" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bookstores" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -35,16 +35,10 @@
     <t>San Francisco</t>
   </si>
   <si>
-    <t>California 94114</t>
-  </si>
-  <si>
     <t>USA</t>
   </si>
   <si>
     <t>1056 Sanchez St</t>
-  </si>
-  <si>
-    <t>California</t>
   </si>
   <si>
     <t>Sanchez</t>
@@ -485,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -496,19 +490,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G2">
         <v>8</v>
@@ -519,19 +513,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>15</v>
@@ -542,19 +536,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4">
         <v>25</v>
@@ -565,19 +559,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -588,19 +582,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -611,19 +605,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>20</v>
